--- a/קטגוריות_ומוצרים.xlsx
+++ b/קטגוריות_ומוצרים.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
   <si>
     <t xml:space="preserve">קטגוריות ומוצרים — מערכת הזמנות בר</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">מוצר</t>
   </si>
   <si>
-    <t xml:space="preserve">💡 הוסף / מחק שורות בחופשיות. לשינוי שם קטגוריה — ערוך את עמודה A. המוצרים יטענו אוטומטית לאפליקציה.</t>
+    <t xml:space="preserve">💡 הוסף / מחק שורות בחופשיות. עמודה A = קטגוריה, עמודה B = מוצר.</t>
   </si>
   <si>
     <t xml:space="preserve">שתייה קלה</t>
@@ -49,13 +49,10 @@
     <t xml:space="preserve">פאנטה</t>
   </si>
   <si>
-    <t xml:space="preserve">מים</t>
+    <t xml:space="preserve">דששדשד</t>
   </si>
   <si>
     <t xml:space="preserve">סודה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">יעןעןלענליח</t>
   </si>
   <si>
     <t xml:space="preserve">ענבים</t>
@@ -573,8 +570,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B35"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="35"/>
@@ -594,7 +591,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
@@ -657,15 +654,15 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4"/>
+      <c r="A13" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="B13" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>15</v>
-      </c>
+      <c r="A14" s="4"/>
       <c r="B14" s="5" t="s">
         <v>16</v>
       </c>
@@ -695,17 +692,17 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4"/>
+      <c r="A19" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="B19" s="5" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="4"/>
+      <c r="B20" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -739,15 +736,15 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4"/>
+      <c r="A26" s="4" t="s">
+        <v>28</v>
+      </c>
       <c r="B26" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
-        <v>29</v>
-      </c>
+      <c r="A27" s="4"/>
       <c r="B27" s="5" t="s">
         <v>30</v>
       </c>
@@ -777,15 +774,15 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4"/>
+      <c r="A32" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="B32" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="s">
-        <v>36</v>
-      </c>
+      <c r="A33" s="4"/>
       <c r="B33" s="5" t="s">
         <v>37</v>
       </c>
@@ -802,21 +799,15 @@
         <v>39</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4"/>
-      <c r="B36" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:A13"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="A20:A26"/>
-    <mergeCell ref="A27:A32"/>
-    <mergeCell ref="A33:A36"/>
+    <mergeCell ref="A4:A12"/>
+    <mergeCell ref="A13:A18"/>
+    <mergeCell ref="A19:A25"/>
+    <mergeCell ref="A26:A31"/>
+    <mergeCell ref="A32:A35"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
